--- a/output/REM_2024_P1_SECCION_D_NODRIZAS.xlsx
+++ b/output/REM_2024_P1_SECCION_D_NODRIZAS.xlsx
@@ -620,16 +620,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -645,7 +637,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -653,30 +645,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -975,63 +949,63 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>132085</v>
       </c>
       <c r="B2">
@@ -1066,7 +1040,7 @@
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>132086</v>
       </c>
       <c r="B3">
@@ -1119,7 +1093,7 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>243654</v>
       </c>
       <c r="B4">
@@ -1157,7 +1131,7 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>243655</v>
       </c>
       <c r="B5">
@@ -1195,7 +1169,7 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>243656</v>
       </c>
       <c r="B6">
@@ -1251,7 +1225,7 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>253961</v>
       </c>
       <c r="B7">
@@ -1310,7 +1284,7 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>262173</v>
       </c>
       <c r="B8">
@@ -1369,7 +1343,7 @@
       </c>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>314708</v>
       </c>
       <c r="B9">
@@ -1428,7 +1402,7 @@
       </c>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>314709</v>
       </c>
       <c r="B10">
@@ -1487,7 +1461,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>314710</v>
       </c>
       <c r="B11">
@@ -1546,7 +1520,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>317667</v>
       </c>
       <c r="B12">
@@ -1605,7 +1579,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>317668</v>
       </c>
       <c r="B13">
@@ -1664,7 +1638,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>317669</v>
       </c>
       <c r="B14">
@@ -1723,7 +1697,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="1">
+      <c r="A15">
         <v>317670</v>
       </c>
       <c r="B15">
@@ -1782,7 +1756,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>457562</v>
       </c>
       <c r="B16">
@@ -1841,7 +1815,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>457563</v>
       </c>
       <c r="B17">
@@ -1900,7 +1874,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>457564</v>
       </c>
       <c r="B18">
@@ -1959,7 +1933,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>457565</v>
       </c>
       <c r="B19">
@@ -2018,7 +1992,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>460091</v>
       </c>
       <c r="B20">
@@ -2077,7 +2051,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>460709</v>
       </c>
       <c r="B21">
@@ -2136,7 +2110,7 @@
       </c>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="1">
+      <c r="A22">
         <v>460710</v>
       </c>
       <c r="B22">
@@ -2195,7 +2169,7 @@
       </c>
     </row>
     <row r="23" spans="1:19">
-      <c r="A23" s="1">
+      <c r="A23">
         <v>460711</v>
       </c>
       <c r="B23">
@@ -2254,7 +2228,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="1">
+      <c r="A24">
         <v>461397</v>
       </c>
       <c r="B24">
@@ -2313,7 +2287,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>461398</v>
       </c>
       <c r="B25">
@@ -2372,7 +2346,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>461399</v>
       </c>
       <c r="B26">
@@ -2431,7 +2405,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="1">
+      <c r="A27">
         <v>461400</v>
       </c>
       <c r="B27">
@@ -2490,7 +2464,7 @@
       </c>
     </row>
     <row r="28" spans="1:19">
-      <c r="A28" s="1">
+      <c r="A28">
         <v>461914</v>
       </c>
       <c r="B28">
@@ -2540,7 +2514,7 @@
       </c>
     </row>
     <row r="29" spans="1:19">
-      <c r="A29" s="1">
+      <c r="A29">
         <v>461915</v>
       </c>
       <c r="B29">
@@ -2590,7 +2564,7 @@
       </c>
     </row>
     <row r="30" spans="1:19">
-      <c r="A30" s="1">
+      <c r="A30">
         <v>461916</v>
       </c>
       <c r="B30">
@@ -2643,7 +2617,7 @@
       </c>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>461917</v>
       </c>
       <c r="B31">
@@ -2696,7 +2670,7 @@
       </c>
     </row>
     <row r="32" spans="1:19">
-      <c r="A32" s="1">
+      <c r="A32">
         <v>462712</v>
       </c>
       <c r="B32">
@@ -2755,7 +2729,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="1">
+      <c r="A33">
         <v>462713</v>
       </c>
       <c r="B33">
@@ -2814,7 +2788,7 @@
       </c>
     </row>
     <row r="34" spans="1:19">
-      <c r="A34" s="1">
+      <c r="A34">
         <v>462714</v>
       </c>
       <c r="B34">
@@ -2873,7 +2847,7 @@
       </c>
     </row>
     <row r="35" spans="1:19">
-      <c r="A35" s="1">
+      <c r="A35">
         <v>464825</v>
       </c>
       <c r="B35">
@@ -2932,7 +2906,7 @@
       </c>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="1">
+      <c r="A36">
         <v>465303</v>
       </c>
       <c r="B36">
@@ -2991,7 +2965,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="1">
+      <c r="A37">
         <v>465304</v>
       </c>
       <c r="B37">
@@ -3050,7 +3024,7 @@
       </c>
     </row>
     <row r="38" spans="1:19">
-      <c r="A38" s="1">
+      <c r="A38">
         <v>465305</v>
       </c>
       <c r="B38">
@@ -3109,7 +3083,7 @@
       </c>
     </row>
     <row r="39" spans="1:19">
-      <c r="A39" s="1">
+      <c r="A39">
         <v>466402</v>
       </c>
       <c r="B39">
@@ -3168,7 +3142,7 @@
       </c>
     </row>
     <row r="40" spans="1:19">
-      <c r="A40" s="1">
+      <c r="A40">
         <v>466403</v>
       </c>
       <c r="B40">
@@ -3227,7 +3201,7 @@
       </c>
     </row>
     <row r="41" spans="1:19">
-      <c r="A41" s="1">
+      <c r="A41">
         <v>466404</v>
       </c>
       <c r="B41">
@@ -3286,7 +3260,7 @@
       </c>
     </row>
     <row r="42" spans="1:19">
-      <c r="A42" s="1">
+      <c r="A42">
         <v>466448</v>
       </c>
       <c r="B42">
@@ -3345,7 +3319,7 @@
       </c>
     </row>
     <row r="43" spans="1:19">
-      <c r="A43" s="1">
+      <c r="A43">
         <v>467199</v>
       </c>
       <c r="B43">
@@ -3404,7 +3378,7 @@
       </c>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="1">
+      <c r="A44">
         <v>467200</v>
       </c>
       <c r="B44">
@@ -3463,7 +3437,7 @@
       </c>
     </row>
     <row r="45" spans="1:19">
-      <c r="A45" s="1">
+      <c r="A45">
         <v>467201</v>
       </c>
       <c r="B45">
@@ -3522,7 +3496,7 @@
       </c>
     </row>
     <row r="46" spans="1:19">
-      <c r="A46" s="1">
+      <c r="A46">
         <v>467613</v>
       </c>
       <c r="B46">
@@ -3581,7 +3555,7 @@
       </c>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="1">
+      <c r="A47">
         <v>467614</v>
       </c>
       <c r="B47">
@@ -3640,7 +3614,7 @@
       </c>
     </row>
     <row r="48" spans="1:19">
-      <c r="A48" s="1">
+      <c r="A48">
         <v>467838</v>
       </c>
       <c r="B48">
@@ -3699,7 +3673,7 @@
       </c>
     </row>
     <row r="49" spans="1:19">
-      <c r="A49" s="1">
+      <c r="A49">
         <v>467839</v>
       </c>
       <c r="B49">
@@ -3758,7 +3732,7 @@
       </c>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="1">
+      <c r="A50">
         <v>467840</v>
       </c>
       <c r="B50">
@@ -3817,7 +3791,7 @@
       </c>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="1">
+      <c r="A51">
         <v>468025</v>
       </c>
       <c r="B51">
@@ -3876,7 +3850,7 @@
       </c>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="1">
+      <c r="A52">
         <v>468911</v>
       </c>
       <c r="B52">
@@ -3911,7 +3885,7 @@
       </c>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="1">
+      <c r="A53">
         <v>468912</v>
       </c>
       <c r="B53">
@@ -3946,7 +3920,7 @@
       </c>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="1">
+      <c r="A54">
         <v>468913</v>
       </c>
       <c r="B54">
@@ -3981,7 +3955,7 @@
       </c>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="1">
+      <c r="A55">
         <v>469529</v>
       </c>
       <c r="B55">
@@ -4040,7 +4014,7 @@
       </c>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="1">
+      <c r="A56">
         <v>470130</v>
       </c>
       <c r="B56">
@@ -4099,7 +4073,7 @@
       </c>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="1">
+      <c r="A57">
         <v>470131</v>
       </c>
       <c r="B57">
@@ -4158,7 +4132,7 @@
       </c>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="1">
+      <c r="A58">
         <v>470132</v>
       </c>
       <c r="B58">
@@ -4217,7 +4191,7 @@
       </c>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="1">
+      <c r="A59">
         <v>470229</v>
       </c>
       <c r="B59">
@@ -4252,7 +4226,7 @@
       </c>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="1">
+      <c r="A60">
         <v>470230</v>
       </c>
       <c r="B60">
@@ -4290,7 +4264,7 @@
       </c>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="1">
+      <c r="A61">
         <v>470231</v>
       </c>
       <c r="B61">
@@ -4325,7 +4299,7 @@
       </c>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="1">
+      <c r="A62">
         <v>471546</v>
       </c>
       <c r="B62">
@@ -4384,7 +4358,7 @@
       </c>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="1">
+      <c r="A63">
         <v>471547</v>
       </c>
       <c r="B63">
@@ -4443,7 +4417,7 @@
       </c>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="1">
+      <c r="A64">
         <v>471548</v>
       </c>
       <c r="B64">
@@ -4502,7 +4476,7 @@
       </c>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="1">
+      <c r="A65">
         <v>471887</v>
       </c>
       <c r="B65">
@@ -4561,7 +4535,7 @@
       </c>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="1">
+      <c r="A66">
         <v>471888</v>
       </c>
       <c r="B66">
@@ -4620,7 +4594,7 @@
       </c>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="1">
+      <c r="A67">
         <v>471889</v>
       </c>
       <c r="B67">
@@ -4679,7 +4653,7 @@
       </c>
     </row>
     <row r="68" spans="1:19">
-      <c r="A68" s="1">
+      <c r="A68">
         <v>473683</v>
       </c>
       <c r="B68">
@@ -4738,7 +4712,7 @@
       </c>
     </row>
     <row r="69" spans="1:19">
-      <c r="A69" s="1">
+      <c r="A69">
         <v>473684</v>
       </c>
       <c r="B69">
@@ -4797,7 +4771,7 @@
       </c>
     </row>
     <row r="70" spans="1:19">
-      <c r="A70" s="1">
+      <c r="A70">
         <v>473999</v>
       </c>
       <c r="B70">
@@ -4856,7 +4830,7 @@
       </c>
     </row>
     <row r="71" spans="1:19">
-      <c r="A71" s="1">
+      <c r="A71">
         <v>474000</v>
       </c>
       <c r="B71">
@@ -4915,7 +4889,7 @@
       </c>
     </row>
     <row r="72" spans="1:19">
-      <c r="A72" s="1">
+      <c r="A72">
         <v>475424</v>
       </c>
       <c r="B72">
@@ -4965,7 +4939,7 @@
       </c>
     </row>
     <row r="73" spans="1:19">
-      <c r="A73" s="1">
+      <c r="A73">
         <v>475425</v>
       </c>
       <c r="B73">
@@ -5015,7 +4989,7 @@
       </c>
     </row>
     <row r="74" spans="1:19">
-      <c r="A74" s="1">
+      <c r="A74">
         <v>475426</v>
       </c>
       <c r="B74">
@@ -5062,7 +5036,7 @@
       </c>
     </row>
     <row r="75" spans="1:19">
-      <c r="A75" s="1">
+      <c r="A75">
         <v>475462</v>
       </c>
       <c r="B75">
@@ -5121,7 +5095,7 @@
       </c>
     </row>
     <row r="76" spans="1:19">
-      <c r="A76" s="1">
+      <c r="A76">
         <v>475463</v>
       </c>
       <c r="B76">
@@ -5180,7 +5154,7 @@
       </c>
     </row>
     <row r="77" spans="1:19">
-      <c r="A77" s="1">
+      <c r="A77">
         <v>475464</v>
       </c>
       <c r="B77">
@@ -5239,7 +5213,7 @@
       </c>
     </row>
     <row r="78" spans="1:19">
-      <c r="A78" s="1">
+      <c r="A78">
         <v>475465</v>
       </c>
       <c r="B78">
@@ -5298,7 +5272,7 @@
       </c>
     </row>
     <row r="79" spans="1:19">
-      <c r="A79" s="1">
+      <c r="A79">
         <v>475553</v>
       </c>
       <c r="B79">
@@ -5357,7 +5331,7 @@
       </c>
     </row>
     <row r="80" spans="1:19">
-      <c r="A80" s="1">
+      <c r="A80">
         <v>475556</v>
       </c>
       <c r="B80">
@@ -5392,7 +5366,7 @@
       </c>
     </row>
     <row r="81" spans="1:19">
-      <c r="A81" s="1">
+      <c r="A81">
         <v>475924</v>
       </c>
       <c r="B81">
@@ -5451,7 +5425,7 @@
       </c>
     </row>
     <row r="82" spans="1:19">
-      <c r="A82" s="1">
+      <c r="A82">
         <v>476218</v>
       </c>
       <c r="B82">
@@ -5492,7 +5466,7 @@
       </c>
     </row>
     <row r="83" spans="1:19">
-      <c r="A83" s="1">
+      <c r="A83">
         <v>476219</v>
       </c>
       <c r="B83">
@@ -5536,7 +5510,7 @@
       </c>
     </row>
     <row r="84" spans="1:19">
-      <c r="A84" s="1">
+      <c r="A84">
         <v>476255</v>
       </c>
       <c r="B84">
@@ -5571,7 +5545,7 @@
       </c>
     </row>
     <row r="85" spans="1:19">
-      <c r="A85" s="1">
+      <c r="A85">
         <v>492144</v>
       </c>
       <c r="B85">
@@ -5612,7 +5586,7 @@
       </c>
     </row>
     <row r="86" spans="1:19">
-      <c r="A86" s="1">
+      <c r="A86">
         <v>492145</v>
       </c>
       <c r="B86">
@@ -5647,7 +5621,7 @@
       </c>
     </row>
     <row r="87" spans="1:19">
-      <c r="A87" s="1">
+      <c r="A87">
         <v>565972</v>
       </c>
       <c r="B87">
@@ -5694,7 +5668,7 @@
       </c>
     </row>
     <row r="88" spans="1:19">
-      <c r="A88" s="1">
+      <c r="A88">
         <v>565973</v>
       </c>
       <c r="B88">
@@ -5744,7 +5718,7 @@
       </c>
     </row>
     <row r="89" spans="1:19">
-      <c r="A89" s="1">
+      <c r="A89">
         <v>565974</v>
       </c>
       <c r="B89">
@@ -5791,7 +5765,7 @@
       </c>
     </row>
     <row r="90" spans="1:19">
-      <c r="A90" s="1">
+      <c r="A90">
         <v>568008</v>
       </c>
       <c r="B90">
@@ -5829,7 +5803,7 @@
       </c>
     </row>
     <row r="91" spans="1:19">
-      <c r="A91" s="1">
+      <c r="A91">
         <v>568009</v>
       </c>
       <c r="B91">
@@ -5864,7 +5838,7 @@
       </c>
     </row>
     <row r="92" spans="1:19">
-      <c r="A92" s="1">
+      <c r="A92">
         <v>569998</v>
       </c>
       <c r="B92">
@@ -5923,7 +5897,7 @@
       </c>
     </row>
     <row r="93" spans="1:19">
-      <c r="A93" s="1">
+      <c r="A93">
         <v>569999</v>
       </c>
       <c r="B93">
@@ -5982,7 +5956,7 @@
       </c>
     </row>
     <row r="94" spans="1:19">
-      <c r="A94" s="1">
+      <c r="A94">
         <v>570000</v>
       </c>
       <c r="B94">
@@ -6041,7 +6015,7 @@
       </c>
     </row>
     <row r="95" spans="1:19">
-      <c r="A95" s="1">
+      <c r="A95">
         <v>571622</v>
       </c>
       <c r="B95">
@@ -6100,7 +6074,7 @@
       </c>
     </row>
     <row r="96" spans="1:19">
-      <c r="A96" s="1">
+      <c r="A96">
         <v>571623</v>
       </c>
       <c r="B96">
@@ -6159,7 +6133,7 @@
       </c>
     </row>
     <row r="97" spans="1:19">
-      <c r="A97" s="1">
+      <c r="A97">
         <v>571624</v>
       </c>
       <c r="B97">
@@ -6218,7 +6192,7 @@
       </c>
     </row>
     <row r="98" spans="1:19">
-      <c r="A98" s="1">
+      <c r="A98">
         <v>571625</v>
       </c>
       <c r="B98">
@@ -6277,7 +6251,7 @@
       </c>
     </row>
     <row r="99" spans="1:19">
-      <c r="A99" s="1">
+      <c r="A99">
         <v>572543</v>
       </c>
       <c r="B99">
@@ -6324,7 +6298,7 @@
       </c>
     </row>
     <row r="100" spans="1:19">
-      <c r="A100" s="1">
+      <c r="A100">
         <v>572544</v>
       </c>
       <c r="B100">
@@ -6371,7 +6345,7 @@
       </c>
     </row>
     <row r="101" spans="1:19">
-      <c r="A101" s="1">
+      <c r="A101">
         <v>572545</v>
       </c>
       <c r="B101">
@@ -6421,7 +6395,7 @@
       </c>
     </row>
     <row r="102" spans="1:19">
-      <c r="A102" s="1">
+      <c r="A102">
         <v>572546</v>
       </c>
       <c r="B102">
@@ -6456,7 +6430,7 @@
       </c>
     </row>
     <row r="103" spans="1:19">
-      <c r="A103" s="1">
+      <c r="A103">
         <v>572805</v>
       </c>
       <c r="B103">
@@ -6515,7 +6489,7 @@
       </c>
     </row>
     <row r="104" spans="1:19">
-      <c r="A104" s="1">
+      <c r="A104">
         <v>572806</v>
       </c>
       <c r="B104">
@@ -6574,7 +6548,7 @@
       </c>
     </row>
     <row r="105" spans="1:19">
-      <c r="A105" s="1">
+      <c r="A105">
         <v>572807</v>
       </c>
       <c r="B105">
@@ -6633,7 +6607,7 @@
       </c>
     </row>
     <row r="106" spans="1:19">
-      <c r="A106" s="1">
+      <c r="A106">
         <v>573763</v>
       </c>
       <c r="B106">
@@ -6692,7 +6666,7 @@
       </c>
     </row>
     <row r="107" spans="1:19">
-      <c r="A107" s="1">
+      <c r="A107">
         <v>574397</v>
       </c>
       <c r="B107">
@@ -6751,7 +6725,7 @@
       </c>
     </row>
     <row r="108" spans="1:19">
-      <c r="A108" s="1">
+      <c r="A108">
         <v>574398</v>
       </c>
       <c r="B108">
@@ -6810,7 +6784,7 @@
       </c>
     </row>
     <row r="109" spans="1:19">
-      <c r="A109" s="1">
+      <c r="A109">
         <v>574399</v>
       </c>
       <c r="B109">
@@ -6869,7 +6843,7 @@
       </c>
     </row>
     <row r="110" spans="1:19">
-      <c r="A110" s="1">
+      <c r="A110">
         <v>574400</v>
       </c>
       <c r="B110">
@@ -6928,7 +6902,7 @@
       </c>
     </row>
     <row r="111" spans="1:19">
-      <c r="A111" s="1">
+      <c r="A111">
         <v>575903</v>
       </c>
       <c r="B111">
@@ -6987,7 +6961,7 @@
       </c>
     </row>
     <row r="112" spans="1:19">
-      <c r="A112" s="1">
+      <c r="A112">
         <v>575904</v>
       </c>
       <c r="B112">
@@ -7046,7 +7020,7 @@
       </c>
     </row>
     <row r="113" spans="1:19">
-      <c r="A113" s="1">
+      <c r="A113">
         <v>577379</v>
       </c>
       <c r="B113">
@@ -7093,7 +7067,7 @@
       </c>
     </row>
     <row r="114" spans="1:19">
-      <c r="A114" s="1">
+      <c r="A114">
         <v>577380</v>
       </c>
       <c r="B114">
@@ -7140,7 +7114,7 @@
       </c>
     </row>
     <row r="115" spans="1:19">
-      <c r="A115" s="1">
+      <c r="A115">
         <v>577381</v>
       </c>
       <c r="B115">
@@ -7187,7 +7161,7 @@
       </c>
     </row>
     <row r="116" spans="1:19">
-      <c r="A116" s="1">
+      <c r="A116">
         <v>577909</v>
       </c>
       <c r="B116">
@@ -7246,7 +7220,7 @@
       </c>
     </row>
     <row r="117" spans="1:19">
-      <c r="A117" s="1">
+      <c r="A117">
         <v>577910</v>
       </c>
       <c r="B117">
@@ -7305,7 +7279,7 @@
       </c>
     </row>
     <row r="118" spans="1:19">
-      <c r="A118" s="1">
+      <c r="A118">
         <v>577911</v>
       </c>
       <c r="B118">
@@ -7364,7 +7338,7 @@
       </c>
     </row>
     <row r="119" spans="1:19">
-      <c r="A119" s="1">
+      <c r="A119">
         <v>577912</v>
       </c>
       <c r="B119">
@@ -7423,7 +7397,7 @@
       </c>
     </row>
     <row r="120" spans="1:19">
-      <c r="A120" s="1">
+      <c r="A120">
         <v>578313</v>
       </c>
       <c r="B120">
@@ -7473,7 +7447,7 @@
       </c>
     </row>
     <row r="121" spans="1:19">
-      <c r="A121" s="1">
+      <c r="A121">
         <v>578314</v>
       </c>
       <c r="B121">
@@ -7523,7 +7497,7 @@
       </c>
     </row>
     <row r="122" spans="1:19">
-      <c r="A122" s="1">
+      <c r="A122">
         <v>578315</v>
       </c>
       <c r="B122">
@@ -7573,7 +7547,7 @@
       </c>
     </row>
     <row r="123" spans="1:19">
-      <c r="A123" s="1">
+      <c r="A123">
         <v>578316</v>
       </c>
       <c r="B123">
@@ -7611,7 +7585,7 @@
       </c>
     </row>
     <row r="124" spans="1:19">
-      <c r="A124" s="1">
+      <c r="A124">
         <v>579144</v>
       </c>
       <c r="B124">
@@ -7649,7 +7623,7 @@
       </c>
     </row>
     <row r="125" spans="1:19">
-      <c r="A125" s="1">
+      <c r="A125">
         <v>579145</v>
       </c>
       <c r="B125">
@@ -7684,7 +7658,7 @@
       </c>
     </row>
     <row r="126" spans="1:19">
-      <c r="A126" s="1">
+      <c r="A126">
         <v>579146</v>
       </c>
       <c r="B126">
@@ -7719,7 +7693,7 @@
       </c>
     </row>
     <row r="127" spans="1:19">
-      <c r="A127" s="1">
+      <c r="A127">
         <v>580079</v>
       </c>
       <c r="B127">
@@ -7754,7 +7728,7 @@
       </c>
     </row>
     <row r="128" spans="1:19">
-      <c r="A128" s="1">
+      <c r="A128">
         <v>580080</v>
       </c>
       <c r="B128">
@@ -7789,7 +7763,7 @@
       </c>
     </row>
     <row r="129" spans="1:19">
-      <c r="A129" s="1">
+      <c r="A129">
         <v>580665</v>
       </c>
       <c r="B129">
@@ -7848,7 +7822,7 @@
       </c>
     </row>
     <row r="130" spans="1:19">
-      <c r="A130" s="1">
+      <c r="A130">
         <v>580666</v>
       </c>
       <c r="B130">
@@ -7907,7 +7881,7 @@
       </c>
     </row>
     <row r="131" spans="1:19">
-      <c r="A131" s="1">
+      <c r="A131">
         <v>580667</v>
       </c>
       <c r="B131">
@@ -7966,7 +7940,7 @@
       </c>
     </row>
     <row r="132" spans="1:19">
-      <c r="A132" s="1">
+      <c r="A132">
         <v>582163</v>
       </c>
       <c r="B132">
@@ -8013,7 +7987,7 @@
       </c>
     </row>
     <row r="133" spans="1:19">
-      <c r="A133" s="1">
+      <c r="A133">
         <v>582164</v>
       </c>
       <c r="B133">
@@ -8060,7 +8034,7 @@
       </c>
     </row>
     <row r="134" spans="1:19">
-      <c r="A134" s="1">
+      <c r="A134">
         <v>582165</v>
       </c>
       <c r="B134">
@@ -8104,7 +8078,7 @@
       </c>
     </row>
     <row r="135" spans="1:19">
-      <c r="A135" s="1">
+      <c r="A135">
         <v>582739</v>
       </c>
       <c r="B135">
@@ -8163,7 +8137,7 @@
       </c>
     </row>
     <row r="136" spans="1:19">
-      <c r="A136" s="1">
+      <c r="A136">
         <v>582740</v>
       </c>
       <c r="B136">
@@ -8222,7 +8196,7 @@
       </c>
     </row>
     <row r="137" spans="1:19">
-      <c r="A137" s="1">
+      <c r="A137">
         <v>583403</v>
       </c>
       <c r="B137">
@@ -8281,7 +8255,7 @@
       </c>
     </row>
     <row r="138" spans="1:19">
-      <c r="A138" s="1">
+      <c r="A138">
         <v>583404</v>
       </c>
       <c r="B138">
@@ -8340,7 +8314,7 @@
       </c>
     </row>
     <row r="139" spans="1:19">
-      <c r="A139" s="1">
+      <c r="A139">
         <v>584204</v>
       </c>
       <c r="B139">
@@ -8381,7 +8355,7 @@
       </c>
     </row>
     <row r="140" spans="1:19">
-      <c r="A140" s="1">
+      <c r="A140">
         <v>584205</v>
       </c>
       <c r="B140">
@@ -8416,7 +8390,7 @@
       </c>
     </row>
     <row r="141" spans="1:19">
-      <c r="A141" s="1">
+      <c r="A141">
         <v>584374</v>
       </c>
       <c r="B141">
@@ -8460,7 +8434,7 @@
       </c>
     </row>
     <row r="142" spans="1:19">
-      <c r="A142" s="1">
+      <c r="A142">
         <v>584375</v>
       </c>
       <c r="B142">
@@ -8498,7 +8472,7 @@
       </c>
     </row>
     <row r="143" spans="1:19">
-      <c r="A143" s="1">
+      <c r="A143">
         <v>584376</v>
       </c>
       <c r="B143">
@@ -8536,7 +8510,7 @@
       </c>
     </row>
     <row r="144" spans="1:19">
-      <c r="A144" s="1">
+      <c r="A144">
         <v>587879</v>
       </c>
       <c r="B144">
@@ -8595,7 +8569,7 @@
       </c>
     </row>
     <row r="145" spans="1:19">
-      <c r="A145" s="1">
+      <c r="A145">
         <v>587880</v>
       </c>
       <c r="B145">
@@ -8654,7 +8628,7 @@
       </c>
     </row>
     <row r="146" spans="1:19">
-      <c r="A146" s="1">
+      <c r="A146">
         <v>587881</v>
       </c>
       <c r="B146">
@@ -8713,7 +8687,7 @@
       </c>
     </row>
     <row r="147" spans="1:19">
-      <c r="A147" s="1">
+      <c r="A147">
         <v>588295</v>
       </c>
       <c r="B147">
@@ -8772,7 +8746,7 @@
       </c>
     </row>
     <row r="148" spans="1:19">
-      <c r="A148" s="1">
+      <c r="A148">
         <v>588296</v>
       </c>
       <c r="B148">
@@ -8831,7 +8805,7 @@
       </c>
     </row>
     <row r="149" spans="1:19">
-      <c r="A149" s="1">
+      <c r="A149">
         <v>588297</v>
       </c>
       <c r="B149">
@@ -8890,7 +8864,7 @@
       </c>
     </row>
     <row r="150" spans="1:19">
-      <c r="A150" s="1">
+      <c r="A150">
         <v>588298</v>
       </c>
       <c r="B150">
@@ -8949,7 +8923,7 @@
       </c>
     </row>
     <row r="151" spans="1:19">
-      <c r="A151" s="1">
+      <c r="A151">
         <v>591067</v>
       </c>
       <c r="B151">
@@ -9008,7 +8982,7 @@
       </c>
     </row>
     <row r="152" spans="1:19">
-      <c r="A152" s="1">
+      <c r="A152">
         <v>591068</v>
       </c>
       <c r="B152">
@@ -9067,7 +9041,7 @@
       </c>
     </row>
     <row r="153" spans="1:19">
-      <c r="A153" s="1">
+      <c r="A153">
         <v>591069</v>
       </c>
       <c r="B153">
@@ -9126,7 +9100,7 @@
       </c>
     </row>
     <row r="154" spans="1:19">
-      <c r="A154" s="1">
+      <c r="A154">
         <v>591998</v>
       </c>
       <c r="B154">
@@ -9167,7 +9141,7 @@
       </c>
     </row>
     <row r="155" spans="1:19">
-      <c r="A155" s="1">
+      <c r="A155">
         <v>591999</v>
       </c>
       <c r="B155">
@@ -9208,7 +9182,7 @@
       </c>
     </row>
     <row r="156" spans="1:19">
-      <c r="A156" s="1">
+      <c r="A156">
         <v>592000</v>
       </c>
       <c r="B156">
@@ -9243,7 +9217,7 @@
       </c>
     </row>
     <row r="157" spans="1:19">
-      <c r="A157" s="1">
+      <c r="A157">
         <v>592621</v>
       </c>
       <c r="B157">
@@ -9302,7 +9276,7 @@
       </c>
     </row>
     <row r="158" spans="1:19">
-      <c r="A158" s="1">
+      <c r="A158">
         <v>592622</v>
       </c>
       <c r="B158">
@@ -9361,7 +9335,7 @@
       </c>
     </row>
     <row r="159" spans="1:19">
-      <c r="A159" s="1">
+      <c r="A159">
         <v>592623</v>
       </c>
       <c r="B159">
@@ -9420,7 +9394,7 @@
       </c>
     </row>
     <row r="160" spans="1:19">
-      <c r="A160" s="1">
+      <c r="A160">
         <v>592816</v>
       </c>
       <c r="B160">
@@ -9458,7 +9432,7 @@
       </c>
     </row>
     <row r="161" spans="1:19">
-      <c r="A161" s="1">
+      <c r="A161">
         <v>592817</v>
       </c>
       <c r="B161">
@@ -9499,7 +9473,7 @@
       </c>
     </row>
     <row r="162" spans="1:19">
-      <c r="A162" s="1">
+      <c r="A162">
         <v>724790</v>
       </c>
       <c r="B162">
@@ -9537,7 +9511,7 @@
       </c>
     </row>
     <row r="163" spans="1:19">
-      <c r="A163" s="1">
+      <c r="A163">
         <v>724791</v>
       </c>
       <c r="B163">
@@ -9581,7 +9555,7 @@
       </c>
     </row>
     <row r="164" spans="1:19">
-      <c r="A164" s="1">
+      <c r="A164">
         <v>724792</v>
       </c>
       <c r="B164">
@@ -9616,7 +9590,7 @@
       </c>
     </row>
     <row r="165" spans="1:19">
-      <c r="A165" s="1">
+      <c r="A165">
         <v>724793</v>
       </c>
       <c r="B165">
@@ -9651,7 +9625,7 @@
       </c>
     </row>
     <row r="166" spans="1:19">
-      <c r="A166" s="1">
+      <c r="A166">
         <v>727616</v>
       </c>
       <c r="B166">
@@ -9710,7 +9684,7 @@
       </c>
     </row>
     <row r="167" spans="1:19">
-      <c r="A167" s="1">
+      <c r="A167">
         <v>727617</v>
       </c>
       <c r="B167">
@@ -9769,7 +9743,7 @@
       </c>
     </row>
     <row r="168" spans="1:19">
-      <c r="A168" s="1">
+      <c r="A168">
         <v>727618</v>
       </c>
       <c r="B168">
@@ -9828,7 +9802,7 @@
       </c>
     </row>
     <row r="169" spans="1:19">
-      <c r="A169" s="1">
+      <c r="A169">
         <v>727619</v>
       </c>
       <c r="B169">
@@ -9887,7 +9861,7 @@
       </c>
     </row>
     <row r="170" spans="1:19">
-      <c r="A170" s="1">
+      <c r="A170">
         <v>728184</v>
       </c>
       <c r="B170">
@@ -9946,7 +9920,7 @@
       </c>
     </row>
     <row r="171" spans="1:19">
-      <c r="A171" s="1">
+      <c r="A171">
         <v>728185</v>
       </c>
       <c r="B171">
@@ -10005,7 +9979,7 @@
       </c>
     </row>
     <row r="172" spans="1:19">
-      <c r="A172" s="1">
+      <c r="A172">
         <v>728186</v>
       </c>
       <c r="B172">
@@ -10061,7 +10035,7 @@
       </c>
     </row>
     <row r="173" spans="1:19">
-      <c r="A173" s="1">
+      <c r="A173">
         <v>728187</v>
       </c>
       <c r="B173">
@@ -10120,7 +10094,7 @@
       </c>
     </row>
     <row r="174" spans="1:19">
-      <c r="A174" s="1">
+      <c r="A174">
         <v>728743</v>
       </c>
       <c r="B174">
@@ -10164,7 +10138,7 @@
       </c>
     </row>
     <row r="175" spans="1:19">
-      <c r="A175" s="1">
+      <c r="A175">
         <v>728744</v>
       </c>
       <c r="B175">
@@ -10208,7 +10182,7 @@
       </c>
     </row>
     <row r="176" spans="1:19">
-      <c r="A176" s="1">
+      <c r="A176">
         <v>728855</v>
       </c>
       <c r="B176">
@@ -10249,7 +10223,7 @@
       </c>
     </row>
     <row r="177" spans="1:19">
-      <c r="A177" s="1">
+      <c r="A177">
         <v>729686</v>
       </c>
       <c r="B177">
@@ -10308,7 +10282,7 @@
       </c>
     </row>
     <row r="178" spans="1:19">
-      <c r="A178" s="1">
+      <c r="A178">
         <v>729687</v>
       </c>
       <c r="B178">
@@ -10367,7 +10341,7 @@
       </c>
     </row>
     <row r="179" spans="1:19">
-      <c r="A179" s="1">
+      <c r="A179">
         <v>729688</v>
       </c>
       <c r="B179">
@@ -10426,7 +10400,7 @@
       </c>
     </row>
     <row r="180" spans="1:19">
-      <c r="A180" s="1">
+      <c r="A180">
         <v>733113</v>
       </c>
       <c r="B180">
@@ -10485,7 +10459,7 @@
       </c>
     </row>
     <row r="181" spans="1:19">
-      <c r="A181" s="1">
+      <c r="A181">
         <v>733114</v>
       </c>
       <c r="B181">
@@ -10544,7 +10518,7 @@
       </c>
     </row>
     <row r="182" spans="1:19">
-      <c r="A182" s="1">
+      <c r="A182">
         <v>733115</v>
       </c>
       <c r="B182">
@@ -10603,7 +10577,7 @@
       </c>
     </row>
     <row r="183" spans="1:19">
-      <c r="A183" s="1">
+      <c r="A183">
         <v>733116</v>
       </c>
       <c r="B183">
@@ -10662,7 +10636,7 @@
       </c>
     </row>
     <row r="184" spans="1:19">
-      <c r="A184" s="1">
+      <c r="A184">
         <v>733823</v>
       </c>
       <c r="B184">
@@ -10721,7 +10695,7 @@
       </c>
     </row>
     <row r="185" spans="1:19">
-      <c r="A185" s="1">
+      <c r="A185">
         <v>734520</v>
       </c>
       <c r="B185">
@@ -10780,7 +10754,7 @@
       </c>
     </row>
     <row r="186" spans="1:19">
-      <c r="A186" s="1">
+      <c r="A186">
         <v>734521</v>
       </c>
       <c r="B186">
@@ -10839,7 +10813,7 @@
       </c>
     </row>
     <row r="187" spans="1:19">
-      <c r="A187" s="1">
+      <c r="A187">
         <v>734522</v>
       </c>
       <c r="B187">
@@ -10898,7 +10872,7 @@
       </c>
     </row>
     <row r="188" spans="1:19">
-      <c r="A188" s="1">
+      <c r="A188">
         <v>734678</v>
       </c>
       <c r="B188">
@@ -10936,7 +10910,7 @@
       </c>
     </row>
     <row r="189" spans="1:19">
-      <c r="A189" s="1">
+      <c r="A189">
         <v>734679</v>
       </c>
       <c r="B189">
@@ -10971,7 +10945,7 @@
       </c>
     </row>
     <row r="190" spans="1:19">
-      <c r="A190" s="1">
+      <c r="A190">
         <v>735478</v>
       </c>
       <c r="B190">
@@ -11030,7 +11004,7 @@
       </c>
     </row>
     <row r="191" spans="1:19">
-      <c r="A191" s="1">
+      <c r="A191">
         <v>735479</v>
       </c>
       <c r="B191">
@@ -11089,7 +11063,7 @@
       </c>
     </row>
     <row r="192" spans="1:19">
-      <c r="A192" s="1">
+      <c r="A192">
         <v>735480</v>
       </c>
       <c r="B192">
@@ -11148,7 +11122,7 @@
       </c>
     </row>
     <row r="193" spans="1:19">
-      <c r="A193" s="1">
+      <c r="A193">
         <v>735481</v>
       </c>
       <c r="B193">
@@ -11207,7 +11181,7 @@
       </c>
     </row>
     <row r="194" spans="1:19">
-      <c r="A194" s="1">
+      <c r="A194">
         <v>737613</v>
       </c>
       <c r="B194">
@@ -11266,7 +11240,7 @@
       </c>
     </row>
     <row r="195" spans="1:19">
-      <c r="A195" s="1">
+      <c r="A195">
         <v>737614</v>
       </c>
       <c r="B195">
@@ -11325,7 +11299,7 @@
       </c>
     </row>
     <row r="196" spans="1:19">
-      <c r="A196" s="1">
+      <c r="A196">
         <v>737615</v>
       </c>
       <c r="B196">
@@ -11384,7 +11358,7 @@
       </c>
     </row>
     <row r="197" spans="1:19">
-      <c r="A197" s="1">
+      <c r="A197">
         <v>737859</v>
       </c>
       <c r="B197">
@@ -11428,7 +11402,7 @@
       </c>
     </row>
     <row r="198" spans="1:19">
-      <c r="A198" s="1">
+      <c r="A198">
         <v>737860</v>
       </c>
       <c r="B198">
@@ -11466,7 +11440,7 @@
       </c>
     </row>
     <row r="199" spans="1:19">
-      <c r="A199" s="1">
+      <c r="A199">
         <v>738936</v>
       </c>
       <c r="B199">
@@ -11513,7 +11487,7 @@
       </c>
     </row>
     <row r="200" spans="1:19">
-      <c r="A200" s="1">
+      <c r="A200">
         <v>738937</v>
       </c>
       <c r="B200">
@@ -11560,7 +11534,7 @@
       </c>
     </row>
     <row r="201" spans="1:19">
-      <c r="A201" s="1">
+      <c r="A201">
         <v>738938</v>
       </c>
       <c r="B201">
@@ -11604,7 +11578,7 @@
       </c>
     </row>
     <row r="202" spans="1:19">
-      <c r="A202" s="1">
+      <c r="A202">
         <v>738939</v>
       </c>
       <c r="B202">
@@ -11639,7 +11613,7 @@
       </c>
     </row>
     <row r="203" spans="1:19">
-      <c r="A203" s="1">
+      <c r="A203">
         <v>740776</v>
       </c>
       <c r="B203">
@@ -11698,7 +11672,7 @@
       </c>
     </row>
     <row r="204" spans="1:19">
-      <c r="A204" s="1">
+      <c r="A204">
         <v>742074</v>
       </c>
       <c r="B204">
@@ -11757,7 +11731,7 @@
       </c>
     </row>
     <row r="205" spans="1:19">
-      <c r="A205" s="1">
+      <c r="A205">
         <v>742075</v>
       </c>
       <c r="B205">
@@ -11816,7 +11790,7 @@
       </c>
     </row>
     <row r="206" spans="1:19">
-      <c r="A206" s="1">
+      <c r="A206">
         <v>742076</v>
       </c>
       <c r="B206">
@@ -11875,7 +11849,7 @@
       </c>
     </row>
     <row r="207" spans="1:19">
-      <c r="A207" s="1">
+      <c r="A207">
         <v>744285</v>
       </c>
       <c r="B207">
@@ -11934,7 +11908,7 @@
       </c>
     </row>
     <row r="208" spans="1:19">
-      <c r="A208" s="1">
+      <c r="A208">
         <v>744286</v>
       </c>
       <c r="B208">
@@ -11993,7 +11967,7 @@
       </c>
     </row>
     <row r="209" spans="1:19">
-      <c r="A209" s="1">
+      <c r="A209">
         <v>744320</v>
       </c>
       <c r="B209">
@@ -12052,7 +12026,7 @@
       </c>
     </row>
     <row r="210" spans="1:19">
-      <c r="A210" s="1">
+      <c r="A210">
         <v>744321</v>
       </c>
       <c r="B210">
@@ -12111,7 +12085,7 @@
       </c>
     </row>
     <row r="211" spans="1:19">
-      <c r="A211" s="1">
+      <c r="A211">
         <v>744322</v>
       </c>
       <c r="B211">
@@ -12170,7 +12144,7 @@
       </c>
     </row>
     <row r="212" spans="1:19">
-      <c r="A212" s="1">
+      <c r="A212">
         <v>744323</v>
       </c>
       <c r="B212">
@@ -12229,7 +12203,7 @@
       </c>
     </row>
     <row r="213" spans="1:19">
-      <c r="A213" s="1">
+      <c r="A213">
         <v>746000</v>
       </c>
       <c r="B213">
@@ -12288,7 +12262,7 @@
       </c>
     </row>
     <row r="214" spans="1:19">
-      <c r="A214" s="1">
+      <c r="A214">
         <v>746001</v>
       </c>
       <c r="B214">
@@ -12347,7 +12321,7 @@
       </c>
     </row>
     <row r="215" spans="1:19">
-      <c r="A215" s="1">
+      <c r="A215">
         <v>746002</v>
       </c>
       <c r="B215">
@@ -12406,7 +12380,7 @@
       </c>
     </row>
     <row r="216" spans="1:19">
-      <c r="A216" s="1">
+      <c r="A216">
         <v>747283</v>
       </c>
       <c r="B216">
@@ -12441,7 +12415,7 @@
       </c>
     </row>
     <row r="217" spans="1:19">
-      <c r="A217" s="1">
+      <c r="A217">
         <v>747284</v>
       </c>
       <c r="B217">
@@ -12476,7 +12450,7 @@
       </c>
     </row>
     <row r="218" spans="1:19">
-      <c r="A218" s="1">
+      <c r="A218">
         <v>747285</v>
       </c>
       <c r="B218">
@@ -12511,7 +12485,7 @@
       </c>
     </row>
     <row r="219" spans="1:19">
-      <c r="A219" s="1">
+      <c r="A219">
         <v>749854</v>
       </c>
       <c r="B219">
@@ -12570,7 +12544,7 @@
       </c>
     </row>
     <row r="220" spans="1:19">
-      <c r="A220" s="1">
+      <c r="A220">
         <v>749855</v>
       </c>
       <c r="B220">
@@ -12629,7 +12603,7 @@
       </c>
     </row>
     <row r="221" spans="1:19">
-      <c r="A221" s="1">
+      <c r="A221">
         <v>749856</v>
       </c>
       <c r="B221">
@@ -12688,7 +12662,7 @@
       </c>
     </row>
     <row r="222" spans="1:19">
-      <c r="A222" s="1">
+      <c r="A222">
         <v>778251</v>
       </c>
       <c r="B222">
@@ -12747,7 +12721,7 @@
       </c>
     </row>
     <row r="223" spans="1:19">
-      <c r="A223" s="1">
+      <c r="A223">
         <v>778577</v>
       </c>
       <c r="B223">
@@ -12806,7 +12780,7 @@
       </c>
     </row>
     <row r="224" spans="1:19">
-      <c r="A224" s="1">
+      <c r="A224">
         <v>778578</v>
       </c>
       <c r="B224">
@@ -12865,7 +12839,7 @@
       </c>
     </row>
     <row r="225" spans="1:19">
-      <c r="A225" s="1">
+      <c r="A225">
         <v>784795</v>
       </c>
       <c r="B225">
@@ -12924,7 +12898,7 @@
       </c>
     </row>
     <row r="226" spans="1:19">
-      <c r="A226" s="1">
+      <c r="A226">
         <v>784796</v>
       </c>
       <c r="B226">
@@ -12983,7 +12957,7 @@
       </c>
     </row>
     <row r="227" spans="1:19">
-      <c r="A227" s="1">
+      <c r="A227">
         <v>784797</v>
       </c>
       <c r="B227">
@@ -13042,7 +13016,7 @@
       </c>
     </row>
     <row r="228" spans="1:19">
-      <c r="A228" s="1">
+      <c r="A228">
         <v>786189</v>
       </c>
       <c r="B228">
@@ -13077,7 +13051,7 @@
       </c>
     </row>
     <row r="229" spans="1:19">
-      <c r="A229" s="1">
+      <c r="A229">
         <v>786190</v>
       </c>
       <c r="B229">
@@ -13118,7 +13092,7 @@
       </c>
     </row>
     <row r="230" spans="1:19">
-      <c r="A230" s="1">
+      <c r="A230">
         <v>786191</v>
       </c>
       <c r="B230">
@@ -13156,7 +13130,7 @@
       </c>
     </row>
     <row r="231" spans="1:19">
-      <c r="A231" s="1">
+      <c r="A231">
         <v>786491</v>
       </c>
       <c r="B231">
@@ -13215,7 +13189,7 @@
       </c>
     </row>
     <row r="232" spans="1:19">
-      <c r="A232" s="1">
+      <c r="A232">
         <v>786492</v>
       </c>
       <c r="B232">
@@ -13274,7 +13248,7 @@
       </c>
     </row>
     <row r="233" spans="1:19">
-      <c r="A233" s="1">
+      <c r="A233">
         <v>786493</v>
       </c>
       <c r="B233">
@@ -13333,7 +13307,7 @@
       </c>
     </row>
     <row r="234" spans="1:19">
-      <c r="A234" s="1">
+      <c r="A234">
         <v>786494</v>
       </c>
       <c r="B234">
@@ -13392,7 +13366,7 @@
       </c>
     </row>
     <row r="235" spans="1:19">
-      <c r="A235" s="1">
+      <c r="A235">
         <v>787874</v>
       </c>
       <c r="B235">
@@ -13439,7 +13413,7 @@
       </c>
     </row>
     <row r="236" spans="1:19">
-      <c r="A236" s="1">
+      <c r="A236">
         <v>787875</v>
       </c>
       <c r="B236">
@@ -13489,7 +13463,7 @@
       </c>
     </row>
     <row r="237" spans="1:19">
-      <c r="A237" s="1">
+      <c r="A237">
         <v>787876</v>
       </c>
       <c r="B237">
@@ -13530,7 +13504,7 @@
       </c>
     </row>
     <row r="238" spans="1:19">
-      <c r="A238" s="1">
+      <c r="A238">
         <v>787877</v>
       </c>
       <c r="B238">
@@ -13571,7 +13545,7 @@
       </c>
     </row>
     <row r="239" spans="1:19">
-      <c r="A239" s="1">
+      <c r="A239">
         <v>787948</v>
       </c>
       <c r="B239">
@@ -13621,7 +13595,7 @@
       </c>
     </row>
     <row r="240" spans="1:19">
-      <c r="A240" s="1">
+      <c r="A240">
         <v>787983</v>
       </c>
       <c r="B240">
@@ -13671,7 +13645,7 @@
       </c>
     </row>
     <row r="241" spans="1:19">
-      <c r="A241" s="1">
+      <c r="A241">
         <v>787984</v>
       </c>
       <c r="B241">
@@ -13718,7 +13692,7 @@
       </c>
     </row>
     <row r="242" spans="1:19">
-      <c r="A242" s="1">
+      <c r="A242">
         <v>787985</v>
       </c>
       <c r="B242">
@@ -13753,7 +13727,7 @@
       </c>
     </row>
     <row r="243" spans="1:19">
-      <c r="A243" s="1">
+      <c r="A243">
         <v>788067</v>
       </c>
       <c r="B243">
@@ -13812,7 +13786,7 @@
       </c>
     </row>
     <row r="244" spans="1:19">
-      <c r="A244" s="1">
+      <c r="A244">
         <v>788068</v>
       </c>
       <c r="B244">
@@ -13871,7 +13845,7 @@
       </c>
     </row>
     <row r="245" spans="1:19">
-      <c r="A245" s="1">
+      <c r="A245">
         <v>789894</v>
       </c>
       <c r="B245">
@@ -13930,7 +13904,7 @@
       </c>
     </row>
     <row r="246" spans="1:19">
-      <c r="A246" s="1">
+      <c r="A246">
         <v>789895</v>
       </c>
       <c r="B246">
@@ -13989,7 +13963,7 @@
       </c>
     </row>
     <row r="247" spans="1:19">
-      <c r="A247" s="1">
+      <c r="A247">
         <v>789896</v>
       </c>
       <c r="B247">
@@ -14048,7 +14022,7 @@
       </c>
     </row>
     <row r="248" spans="1:19">
-      <c r="A248" s="1">
+      <c r="A248">
         <v>790330</v>
       </c>
       <c r="B248">
@@ -14107,7 +14081,7 @@
       </c>
     </row>
     <row r="249" spans="1:19">
-      <c r="A249" s="1">
+      <c r="A249">
         <v>790331</v>
       </c>
       <c r="B249">
@@ -14166,7 +14140,7 @@
       </c>
     </row>
     <row r="250" spans="1:19">
-      <c r="A250" s="1">
+      <c r="A250">
         <v>790332</v>
       </c>
       <c r="B250">
@@ -14225,7 +14199,7 @@
       </c>
     </row>
     <row r="251" spans="1:19">
-      <c r="A251" s="1">
+      <c r="A251">
         <v>791508</v>
       </c>
       <c r="B251">
@@ -14263,7 +14237,7 @@
       </c>
     </row>
     <row r="252" spans="1:19">
-      <c r="A252" s="1">
+      <c r="A252">
         <v>791509</v>
       </c>
       <c r="B252">
@@ -14298,7 +14272,7 @@
       </c>
     </row>
     <row r="253" spans="1:19">
-      <c r="A253" s="1">
+      <c r="A253">
         <v>791986</v>
       </c>
       <c r="B253">
@@ -14333,7 +14307,7 @@
       </c>
     </row>
     <row r="254" spans="1:19">
-      <c r="A254" s="1">
+      <c r="A254">
         <v>792717</v>
       </c>
       <c r="B254">
@@ -14392,7 +14366,7 @@
       </c>
     </row>
     <row r="255" spans="1:19">
-      <c r="A255" s="1">
+      <c r="A255">
         <v>792718</v>
       </c>
       <c r="B255">
@@ -14451,7 +14425,7 @@
       </c>
     </row>
     <row r="256" spans="1:19">
-      <c r="A256" s="1">
+      <c r="A256">
         <v>792719</v>
       </c>
       <c r="B256">
@@ -14510,7 +14484,7 @@
       </c>
     </row>
     <row r="257" spans="1:19">
-      <c r="A257" s="1">
+      <c r="A257">
         <v>793577</v>
       </c>
       <c r="B257">
@@ -14569,7 +14543,7 @@
       </c>
     </row>
     <row r="258" spans="1:19">
-      <c r="A258" s="1">
+      <c r="A258">
         <v>793578</v>
       </c>
       <c r="B258">
@@ -14628,7 +14602,7 @@
       </c>
     </row>
     <row r="259" spans="1:19">
-      <c r="A259" s="1">
+      <c r="A259">
         <v>793680</v>
       </c>
       <c r="B259">
@@ -14687,7 +14661,7 @@
       </c>
     </row>
     <row r="260" spans="1:19">
-      <c r="A260" s="1">
+      <c r="A260">
         <v>793902</v>
       </c>
       <c r="B260">
@@ -14731,7 +14705,7 @@
       </c>
     </row>
     <row r="261" spans="1:19">
-      <c r="A261" s="1">
+      <c r="A261">
         <v>793903</v>
       </c>
       <c r="B261">
@@ -14766,7 +14740,7 @@
       </c>
     </row>
     <row r="262" spans="1:19">
-      <c r="A262" s="1">
+      <c r="A262">
         <v>793904</v>
       </c>
       <c r="B262">
@@ -14801,7 +14775,7 @@
       </c>
     </row>
     <row r="263" spans="1:19">
-      <c r="A263" s="1">
+      <c r="A263">
         <v>795901</v>
       </c>
       <c r="B263">
@@ -14848,7 +14822,7 @@
       </c>
     </row>
     <row r="264" spans="1:19">
-      <c r="A264" s="1">
+      <c r="A264">
         <v>795902</v>
       </c>
       <c r="B264">
@@ -14898,7 +14872,7 @@
       </c>
     </row>
     <row r="265" spans="1:19">
-      <c r="A265" s="1">
+      <c r="A265">
         <v>795903</v>
       </c>
       <c r="B265">
@@ -14945,7 +14919,7 @@
       </c>
     </row>
     <row r="266" spans="1:19">
-      <c r="A266" s="1">
+      <c r="A266">
         <v>795904</v>
       </c>
       <c r="B266">
@@ -14980,7 +14954,7 @@
       </c>
     </row>
     <row r="267" spans="1:19">
-      <c r="A267" s="1">
+      <c r="A267">
         <v>813887</v>
       </c>
       <c r="B267">
@@ -15018,7 +14992,7 @@
       </c>
     </row>
     <row r="268" spans="1:19">
-      <c r="A268" s="1">
+      <c r="A268">
         <v>813888</v>
       </c>
       <c r="B268">
@@ -15056,7 +15030,7 @@
       </c>
     </row>
     <row r="269" spans="1:19">
-      <c r="A269" s="1">
+      <c r="A269">
         <v>813889</v>
       </c>
       <c r="B269">
@@ -15091,7 +15065,7 @@
       </c>
     </row>
     <row r="270" spans="1:19">
-      <c r="A270" s="1">
+      <c r="A270">
         <v>814634</v>
       </c>
       <c r="B270">
@@ -15150,7 +15124,7 @@
       </c>
     </row>
     <row r="271" spans="1:19">
-      <c r="A271" s="1">
+      <c r="A271">
         <v>814635</v>
       </c>
       <c r="B271">
@@ -15209,7 +15183,7 @@
       </c>
     </row>
     <row r="272" spans="1:19">
-      <c r="A272" s="1">
+      <c r="A272">
         <v>814636</v>
       </c>
       <c r="B272">
@@ -15268,7 +15242,7 @@
       </c>
     </row>
     <row r="273" spans="1:19">
-      <c r="A273" s="1">
+      <c r="A273">
         <v>953195</v>
       </c>
       <c r="B273">
@@ -15327,7 +15301,7 @@
       </c>
     </row>
     <row r="274" spans="1:19">
-      <c r="A274" s="1">
+      <c r="A274">
         <v>954910</v>
       </c>
       <c r="B274">
@@ -15365,7 +15339,7 @@
       </c>
     </row>
     <row r="275" spans="1:19">
-      <c r="A275" s="1">
+      <c r="A275">
         <v>954911</v>
       </c>
       <c r="B275">
@@ -15406,7 +15380,7 @@
       </c>
     </row>
     <row r="276" spans="1:19">
-      <c r="A276" s="1">
+      <c r="A276">
         <v>954912</v>
       </c>
       <c r="B276">
@@ -15441,7 +15415,7 @@
       </c>
     </row>
     <row r="277" spans="1:19">
-      <c r="A277" s="1">
+      <c r="A277">
         <v>955979</v>
       </c>
       <c r="B277">
@@ -15500,7 +15474,7 @@
       </c>
     </row>
     <row r="278" spans="1:19">
-      <c r="A278" s="1">
+      <c r="A278">
         <v>955980</v>
       </c>
       <c r="B278">
@@ -15559,7 +15533,7 @@
       </c>
     </row>
     <row r="279" spans="1:19">
-      <c r="A279" s="1">
+      <c r="A279">
         <v>955981</v>
       </c>
       <c r="B279">
@@ -15618,7 +15592,7 @@
       </c>
     </row>
     <row r="280" spans="1:19">
-      <c r="A280" s="1">
+      <c r="A280">
         <v>955994</v>
       </c>
       <c r="B280">
@@ -15677,7 +15651,7 @@
       </c>
     </row>
     <row r="281" spans="1:19">
-      <c r="A281" s="1">
+      <c r="A281">
         <v>958171</v>
       </c>
       <c r="B281">
@@ -15736,7 +15710,7 @@
       </c>
     </row>
     <row r="282" spans="1:19">
-      <c r="A282" s="1">
+      <c r="A282">
         <v>958759</v>
       </c>
       <c r="B282">
@@ -15795,7 +15769,7 @@
       </c>
     </row>
     <row r="283" spans="1:19">
-      <c r="A283" s="1">
+      <c r="A283">
         <v>958835</v>
       </c>
       <c r="B283">
@@ -15854,7 +15828,7 @@
       </c>
     </row>
     <row r="284" spans="1:19">
-      <c r="A284" s="1">
+      <c r="A284">
         <v>958836</v>
       </c>
       <c r="B284">
@@ -15913,7 +15887,7 @@
       </c>
     </row>
     <row r="285" spans="1:19">
-      <c r="A285" s="1">
+      <c r="A285">
         <v>960726</v>
       </c>
       <c r="B285">
@@ -15948,7 +15922,7 @@
       </c>
     </row>
     <row r="286" spans="1:19">
-      <c r="A286" s="1">
+      <c r="A286">
         <v>960727</v>
       </c>
       <c r="B286">
@@ -15995,7 +15969,7 @@
       </c>
     </row>
     <row r="287" spans="1:19">
-      <c r="A287" s="1">
+      <c r="A287">
         <v>960728</v>
       </c>
       <c r="B287">
@@ -16030,7 +16004,7 @@
       </c>
     </row>
     <row r="288" spans="1:19">
-      <c r="A288" s="1">
+      <c r="A288">
         <v>962142</v>
       </c>
       <c r="B288">
@@ -16068,7 +16042,7 @@
       </c>
     </row>
     <row r="289" spans="1:19">
-      <c r="A289" s="1">
+      <c r="A289">
         <v>962143</v>
       </c>
       <c r="B289">
@@ -16103,7 +16077,7 @@
       </c>
     </row>
     <row r="290" spans="1:19">
-      <c r="A290" s="1">
+      <c r="A290">
         <v>962248</v>
       </c>
       <c r="B290">
@@ -16150,7 +16124,7 @@
       </c>
     </row>
     <row r="291" spans="1:19">
-      <c r="A291" s="1">
+      <c r="A291">
         <v>962939</v>
       </c>
       <c r="B291">
@@ -16209,7 +16183,7 @@
       </c>
     </row>
     <row r="292" spans="1:19">
-      <c r="A292" s="1">
+      <c r="A292">
         <v>962940</v>
       </c>
       <c r="B292">
@@ -16268,7 +16242,7 @@
       </c>
     </row>
     <row r="293" spans="1:19">
-      <c r="A293" s="1">
+      <c r="A293">
         <v>962941</v>
       </c>
       <c r="B293">
@@ -16327,7 +16301,7 @@
       </c>
     </row>
     <row r="294" spans="1:19">
-      <c r="A294" s="1">
+      <c r="A294">
         <v>963496</v>
       </c>
       <c r="B294">
@@ -16371,7 +16345,7 @@
       </c>
     </row>
     <row r="295" spans="1:19">
-      <c r="A295" s="1">
+      <c r="A295">
         <v>963497</v>
       </c>
       <c r="B295">
@@ -16421,7 +16395,7 @@
       </c>
     </row>
     <row r="296" spans="1:19">
-      <c r="A296" s="1">
+      <c r="A296">
         <v>963731</v>
       </c>
       <c r="B296">
@@ -16480,7 +16454,7 @@
       </c>
     </row>
     <row r="297" spans="1:19">
-      <c r="A297" s="1">
+      <c r="A297">
         <v>963732</v>
       </c>
       <c r="B297">
@@ -16539,7 +16513,7 @@
       </c>
     </row>
     <row r="298" spans="1:19">
-      <c r="A298" s="1">
+      <c r="A298">
         <v>963733</v>
       </c>
       <c r="B298">
@@ -16598,7 +16572,7 @@
       </c>
     </row>
     <row r="299" spans="1:19">
-      <c r="A299" s="1">
+      <c r="A299">
         <v>964480</v>
       </c>
       <c r="B299">
@@ -16633,7 +16607,7 @@
       </c>
     </row>
     <row r="300" spans="1:19">
-      <c r="A300" s="1">
+      <c r="A300">
         <v>964481</v>
       </c>
       <c r="B300">
@@ -16683,7 +16657,7 @@
       </c>
     </row>
     <row r="301" spans="1:19">
-      <c r="A301" s="1">
+      <c r="A301">
         <v>965353</v>
       </c>
       <c r="B301">
@@ -16718,7 +16692,7 @@
       </c>
     </row>
     <row r="302" spans="1:19">
-      <c r="A302" s="1">
+      <c r="A302">
         <v>965354</v>
       </c>
       <c r="B302">
@@ -16753,7 +16727,7 @@
       </c>
     </row>
     <row r="303" spans="1:19">
-      <c r="A303" s="1">
+      <c r="A303">
         <v>965355</v>
       </c>
       <c r="B303">
@@ -16803,7 +16777,7 @@
       </c>
     </row>
     <row r="304" spans="1:19">
-      <c r="A304" s="1">
+      <c r="A304">
         <v>965697</v>
       </c>
       <c r="B304">
@@ -16841,7 +16815,7 @@
       </c>
     </row>
     <row r="305" spans="1:19">
-      <c r="A305" s="1">
+      <c r="A305">
         <v>965698</v>
       </c>
       <c r="B305">
@@ -16876,7 +16850,7 @@
       </c>
     </row>
     <row r="306" spans="1:19">
-      <c r="A306" s="1">
+      <c r="A306">
         <v>965769</v>
       </c>
       <c r="B306">
@@ -16923,7 +16897,7 @@
       </c>
     </row>
     <row r="307" spans="1:19">
-      <c r="A307" s="1">
+      <c r="A307">
         <v>967042</v>
       </c>
       <c r="B307">
@@ -16964,7 +16938,7 @@
       </c>
     </row>
     <row r="308" spans="1:19">
-      <c r="A308" s="1">
+      <c r="A308">
         <v>967043</v>
       </c>
       <c r="B308">
@@ -16999,7 +16973,7 @@
       </c>
     </row>
     <row r="309" spans="1:19">
-      <c r="A309" s="1">
+      <c r="A309">
         <v>967044</v>
       </c>
       <c r="B309">
@@ -17034,7 +17008,7 @@
       </c>
     </row>
     <row r="310" spans="1:19">
-      <c r="A310" s="1">
+      <c r="A310">
         <v>967439</v>
       </c>
       <c r="B310">
@@ -17093,7 +17067,7 @@
       </c>
     </row>
     <row r="311" spans="1:19">
-      <c r="A311" s="1">
+      <c r="A311">
         <v>967440</v>
       </c>
       <c r="B311">
@@ -17152,7 +17126,7 @@
       </c>
     </row>
     <row r="312" spans="1:19">
-      <c r="A312" s="1">
+      <c r="A312">
         <v>967441</v>
       </c>
       <c r="B312">
@@ -17211,7 +17185,7 @@
       </c>
     </row>
     <row r="313" spans="1:19">
-      <c r="A313" s="1">
+      <c r="A313">
         <v>967442</v>
       </c>
       <c r="B313">
@@ -17270,7 +17244,7 @@
       </c>
     </row>
     <row r="314" spans="1:19">
-      <c r="A314" s="1">
+      <c r="A314">
         <v>969354</v>
       </c>
       <c r="B314">
@@ -17305,7 +17279,7 @@
       </c>
     </row>
     <row r="315" spans="1:19">
-      <c r="A315" s="1">
+      <c r="A315">
         <v>969502</v>
       </c>
       <c r="B315">
@@ -17364,7 +17338,7 @@
       </c>
     </row>
     <row r="316" spans="1:19">
-      <c r="A316" s="1">
+      <c r="A316">
         <v>969852</v>
       </c>
       <c r="B316">
@@ -17423,7 +17397,7 @@
       </c>
     </row>
     <row r="317" spans="1:19">
-      <c r="A317" s="1">
+      <c r="A317">
         <v>969853</v>
       </c>
       <c r="B317">
@@ -17482,7 +17456,7 @@
       </c>
     </row>
     <row r="318" spans="1:19">
-      <c r="A318" s="1">
+      <c r="A318">
         <v>969854</v>
       </c>
       <c r="B318">
@@ -17541,7 +17515,7 @@
       </c>
     </row>
     <row r="319" spans="1:19">
-      <c r="A319" s="1">
+      <c r="A319">
         <v>972516</v>
       </c>
       <c r="B319">
@@ -17600,7 +17574,7 @@
       </c>
     </row>
     <row r="320" spans="1:19">
-      <c r="A320" s="1">
+      <c r="A320">
         <v>972517</v>
       </c>
       <c r="B320">
@@ -17659,7 +17633,7 @@
       </c>
     </row>
     <row r="321" spans="1:19">
-      <c r="A321" s="1">
+      <c r="A321">
         <v>972885</v>
       </c>
       <c r="B321">
@@ -17718,7 +17692,7 @@
       </c>
     </row>
     <row r="322" spans="1:19">
-      <c r="A322" s="1">
+      <c r="A322">
         <v>972921</v>
       </c>
       <c r="B322">
@@ -17777,7 +17751,7 @@
       </c>
     </row>
     <row r="323" spans="1:19">
-      <c r="A323" s="1">
+      <c r="A323">
         <v>976535</v>
       </c>
       <c r="B323">
@@ -17836,7 +17810,7 @@
       </c>
     </row>
     <row r="324" spans="1:19">
-      <c r="A324" s="1">
+      <c r="A324">
         <v>976536</v>
       </c>
       <c r="B324">
@@ -17895,7 +17869,7 @@
       </c>
     </row>
     <row r="325" spans="1:19">
-      <c r="A325" s="1">
+      <c r="A325">
         <v>976537</v>
       </c>
       <c r="B325">
@@ -17954,7 +17928,7 @@
       </c>
     </row>
     <row r="326" spans="1:19">
-      <c r="A326" s="1">
+      <c r="A326">
         <v>980097</v>
       </c>
       <c r="B326">
@@ -17989,7 +17963,7 @@
       </c>
     </row>
     <row r="327" spans="1:19">
-      <c r="A327" s="1">
+      <c r="A327">
         <v>980199</v>
       </c>
       <c r="B327">
@@ -18048,7 +18022,7 @@
       </c>
     </row>
     <row r="328" spans="1:19">
-      <c r="A328" s="1">
+      <c r="A328">
         <v>980200</v>
       </c>
       <c r="B328">
@@ -18107,7 +18081,7 @@
       </c>
     </row>
     <row r="329" spans="1:19">
-      <c r="A329" s="1">
+      <c r="A329">
         <v>980201</v>
       </c>
       <c r="B329">
@@ -18166,7 +18140,7 @@
       </c>
     </row>
     <row r="330" spans="1:19">
-      <c r="A330" s="1">
+      <c r="A330">
         <v>981358</v>
       </c>
       <c r="B330">
@@ -18201,7 +18175,7 @@
       </c>
     </row>
     <row r="331" spans="1:19">
-      <c r="A331" s="1">
+      <c r="A331">
         <v>983170</v>
       </c>
       <c r="B331">
@@ -18248,7 +18222,7 @@
       </c>
     </row>
     <row r="332" spans="1:19">
-      <c r="A332" s="1">
+      <c r="A332">
         <v>983171</v>
       </c>
       <c r="B332">
@@ -18292,7 +18266,7 @@
       </c>
     </row>
     <row r="333" spans="1:19">
-      <c r="A333" s="1">
+      <c r="A333">
         <v>983172</v>
       </c>
       <c r="B333">
@@ -18330,7 +18304,7 @@
       </c>
     </row>
     <row r="334" spans="1:19">
-      <c r="A334" s="1">
+      <c r="A334">
         <v>985610</v>
       </c>
       <c r="B334">
@@ -18365,7 +18339,7 @@
       </c>
     </row>
     <row r="335" spans="1:19">
-      <c r="A335" s="1">
+      <c r="A335">
         <v>985611</v>
       </c>
       <c r="B335">
@@ -18403,7 +18377,7 @@
       </c>
     </row>
     <row r="336" spans="1:19">
-      <c r="A336" s="1">
+      <c r="A336">
         <v>985612</v>
       </c>
       <c r="B336">
@@ -18438,7 +18412,7 @@
       </c>
     </row>
     <row r="337" spans="1:19">
-      <c r="A337" s="1">
+      <c r="A337">
         <v>986063</v>
       </c>
       <c r="B337">
@@ -18497,7 +18471,7 @@
       </c>
     </row>
     <row r="338" spans="1:19">
-      <c r="A338" s="1">
+      <c r="A338">
         <v>986064</v>
       </c>
       <c r="B338">
@@ -18556,7 +18530,7 @@
       </c>
     </row>
     <row r="339" spans="1:19">
-      <c r="A339" s="1">
+      <c r="A339">
         <v>986065</v>
       </c>
       <c r="B339">
@@ -18615,7 +18589,7 @@
       </c>
     </row>
     <row r="340" spans="1:19">
-      <c r="A340" s="1">
+      <c r="A340">
         <v>986325</v>
       </c>
       <c r="B340">
@@ -18650,7 +18624,7 @@
       </c>
     </row>
     <row r="341" spans="1:19">
-      <c r="A341" s="1">
+      <c r="A341">
         <v>986326</v>
       </c>
       <c r="B341">
@@ -18688,7 +18662,7 @@
       </c>
     </row>
     <row r="342" spans="1:19">
-      <c r="A342" s="1">
+      <c r="A342">
         <v>986649</v>
       </c>
       <c r="B342">
@@ -18723,7 +18697,7 @@
       </c>
     </row>
     <row r="343" spans="1:19">
-      <c r="A343" s="1">
+      <c r="A343">
         <v>987243</v>
       </c>
       <c r="B343">
@@ -18761,7 +18735,7 @@
       </c>
     </row>
     <row r="344" spans="1:19">
-      <c r="A344" s="1">
+      <c r="A344">
         <v>987244</v>
       </c>
       <c r="B344">
@@ -18796,7 +18770,7 @@
       </c>
     </row>
     <row r="345" spans="1:19">
-      <c r="A345" s="1">
+      <c r="A345">
         <v>987869</v>
       </c>
       <c r="B345">
@@ -18834,7 +18808,7 @@
       </c>
     </row>
     <row r="346" spans="1:19">
-      <c r="A346" s="1">
+      <c r="A346">
         <v>987870</v>
       </c>
       <c r="B346">
@@ -18872,7 +18846,7 @@
       </c>
     </row>
     <row r="347" spans="1:19">
-      <c r="A347" s="1">
+      <c r="A347">
         <v>988815</v>
       </c>
       <c r="B347">
@@ -18907,7 +18881,7 @@
       </c>
     </row>
     <row r="348" spans="1:19">
-      <c r="A348" s="1">
+      <c r="A348">
         <v>988816</v>
       </c>
       <c r="B348">
@@ -18951,7 +18925,7 @@
       </c>
     </row>
     <row r="349" spans="1:19">
-      <c r="A349" s="1">
+      <c r="A349">
         <v>988817</v>
       </c>
       <c r="B349">
